--- a/jogos_2025-01-21.xlsx
+++ b/jogos_2025-01-21.xlsx
@@ -643,109 +643,109 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['79', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="AH2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['33', '39', '51', '83', '85']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45678.35416666666</v>
@@ -772,23 +772,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.2</v>
       </c>
-      <c r="N3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['33', '39', '51', '83', '85']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.09</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['79', '90+6']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>2</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="AI3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>4.33</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45678.35416666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
         <v>1.8</v>
       </c>
       <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.7</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
         <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
         <v>2.5</v>
@@ -1501,25 +1501,25 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['35', '59']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45678.45833333334</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,55 +1572,55 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.1</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
         <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S9" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
         <v>2.5</v>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['35', '59']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45678.45833333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>17.92</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>19.45</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>3.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.65</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>2.25</v>
+        <v>8.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.63</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['7', '11', '82', '90+1']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>7.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45678.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="M15" t="n">
-        <v>17.92</v>
-      </c>
-      <c r="N15" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="P15" t="n">
-        <v>3.65</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2.13</v>
       </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
-        <v>8.5</v>
+        <v>2.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>1.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.3</v>
+        <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['7', '11', '82', '90+1']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>7.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45678.58333333334</v>
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>2.37</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.67</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AJ17" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['12', '58', '63', '90', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45678.61458333334</v>
@@ -2707,16 +2707,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['12', '58', '63', '90', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.04</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.68</v>
+        <v>4.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45678.61458333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
         <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.3</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['64', '70']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45678.69791666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M21" t="n">
         <v>3.4</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R21" t="n">
         <v>1.44</v>
@@ -3153,28 +3153,28 @@
         <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
         <v>2.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3183,20 +3183,20 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45678.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
         <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
         <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Z22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['71', '86']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AI22" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45678.69791666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O23" t="n">
         <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['33', '68']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['64', '70']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45678.69791666666</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3496,10 +3496,10 @@
         <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
         <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['71', '86']</t>
+          <t>['34', '59']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45678.69791666666</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
         <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['34', '59']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45678.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,48 +3739,48 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.3</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
@@ -3795,25 +3795,25 @@
         <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
         <v>1.62</v>
@@ -3823,25 +3823,25 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['33', '68']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['17', '56']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45678.69791666666</v>
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y28" t="n">
         <v>2.1</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['22', '59', '69']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['11', '26']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45678.69791666666</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,37 +4152,37 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
         <v>1.33</v>
@@ -4191,44 +4191,44 @@
         <v>3.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['29', '83']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['17', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45678.69791666666</v>
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -4273,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
         <v>2.62</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.1</v>
       </c>
       <c r="R30" t="n">
         <v>1.4</v>
@@ -4305,13 +4305,13 @@
         <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
         <v>1.35</v>
@@ -4320,44 +4320,44 @@
         <v>3.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['22', '59', '69']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['11', '26']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['47', '68']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45678.69791666666</v>
@@ -4384,19 +4384,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
         <v>2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -4410,22 +4410,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="M31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.5</v>
       </c>
-      <c r="N31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
@@ -4440,13 +4440,13 @@
         <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y31" t="n">
         <v>1.95</v>
@@ -4455,38 +4455,38 @@
         <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB31" t="n">
         <v>1.28</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['47', '68']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['29', '83']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45678.69791666666</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4528,94 +4528,94 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>8.5</v>
+        <v>2.87</v>
       </c>
       <c r="O32" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="T32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['52', '90']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['34', '67']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45678.70833333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.75</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1.5</v>
       </c>
-      <c r="S33" t="n">
+      <c r="AD33" t="n">
         <v>2.5</v>
       </c>
-      <c r="T33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['71', '77']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['17', '23', '43']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['2', '19']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['45+1', '90+7']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45678.70833333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4786,10 +4786,10 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="M34" t="n">
+        <v>6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['34', '67']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH34" t="n">
         <v>3.5</v>
       </c>
-      <c r="N34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['71', '72']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI34" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.57</v>
+        <v>4.33</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45678.70833333334</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="V35" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '36', '87']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45678.70833333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S37" t="n">
         <v>2.5</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="T37" t="n">
         <v>3.4</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['52', '90']</t>
+          <t>['2', '19']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['45+1', '90+7']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45678.70833333334</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
         <v>1</v>
       </c>
-      <c r="H38" t="n">
-        <v>3</v>
-      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.67</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['71', '72']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['11', '36', '87']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45678.70833333334</v>
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>4</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="n">
+      <c r="Z39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.8</v>
       </c>
-      <c r="O39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X39" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD39" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['71', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['17', '23', '43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45678.70833333334</v>
